--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,16 @@
           <t>Radius</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -450,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.43695</v>
+        <v>16.70875</v>
       </c>
       <c r="D2" t="n">
-        <v>16.45941</v>
+        <v>16.43285</v>
       </c>
       <c r="E2" t="n">
-        <v>16.69101</v>
+        <v>16.60411</v>
       </c>
       <c r="F2" t="n">
-        <v>42.33529</v>
+        <v>42.78352</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05029</v>
+        <v>0.04982</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83244</v>
+        <v>1.81594</v>
       </c>
     </row>
     <row r="3">
@@ -475,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.90972</v>
+        <v>16.75143</v>
       </c>
       <c r="D3" t="n">
-        <v>16.91862</v>
+        <v>16.62472</v>
       </c>
       <c r="E3" t="n">
-        <v>16.76897</v>
+        <v>16.7297</v>
       </c>
       <c r="F3" t="n">
-        <v>42.56315</v>
+        <v>42.83678</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05018</v>
+        <v>0.05076</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84576</v>
+        <v>1.82321</v>
       </c>
     </row>
     <row r="4">
@@ -500,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.96397</v>
+        <v>16.76344</v>
       </c>
       <c r="D4" t="n">
-        <v>16.48518</v>
+        <v>16.60896</v>
       </c>
       <c r="E4" t="n">
-        <v>17.14063</v>
+        <v>16.72487</v>
       </c>
       <c r="F4" t="n">
-        <v>42.41638</v>
+        <v>43.10346</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05089</v>
+        <v>0.05059</v>
       </c>
       <c r="H4" t="n">
-        <v>1.80564</v>
+        <v>1.81331</v>
       </c>
     </row>
     <row r="5">
@@ -525,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.76723</v>
+        <v>16.97358</v>
       </c>
       <c r="D5" t="n">
-        <v>16.52364</v>
+        <v>16.55129</v>
       </c>
       <c r="E5" t="n">
-        <v>16.58095</v>
+        <v>16.80581</v>
       </c>
       <c r="F5" t="n">
-        <v>42.93984</v>
+        <v>41.92713</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05026</v>
+        <v>0.05056</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7921</v>
+        <v>1.83679</v>
       </c>
     </row>
     <row r="6">
@@ -550,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.77425</v>
+        <v>16.72837</v>
       </c>
       <c r="D6" t="n">
-        <v>16.71453</v>
+        <v>16.63626</v>
       </c>
       <c r="E6" t="n">
-        <v>16.75854</v>
+        <v>16.70231</v>
       </c>
       <c r="F6" t="n">
-        <v>42.57686</v>
+        <v>42.06687</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05045</v>
+        <v>0.05048</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83405</v>
+        <v>1.7829</v>
       </c>
     </row>
     <row r="7">
@@ -575,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.83663</v>
+        <v>16.9268</v>
       </c>
       <c r="D7" t="n">
-        <v>16.66869</v>
+        <v>16.4569</v>
       </c>
       <c r="E7" t="n">
-        <v>16.8222</v>
+        <v>16.80021</v>
       </c>
       <c r="F7" t="n">
-        <v>42.67765</v>
+        <v>42.16135</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05078</v>
+        <v>0.04981</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8107</v>
+        <v>1.82861</v>
       </c>
     </row>
     <row r="8">
@@ -600,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.00059</v>
+        <v>16.96588</v>
       </c>
       <c r="D8" t="n">
-        <v>16.83435</v>
+        <v>16.45311</v>
       </c>
       <c r="E8" t="n">
-        <v>16.66394</v>
+        <v>16.76608</v>
       </c>
       <c r="F8" t="n">
-        <v>42.92885</v>
+        <v>42.47153</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05104</v>
+        <v>0.05023</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82705</v>
+        <v>1.8204</v>
       </c>
     </row>
     <row r="9">
@@ -625,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.91144</v>
+        <v>16.98146</v>
       </c>
       <c r="D9" t="n">
-        <v>16.53647</v>
+        <v>16.41821</v>
       </c>
       <c r="E9" t="n">
-        <v>16.7385</v>
+        <v>16.71924</v>
       </c>
       <c r="F9" t="n">
-        <v>42.8068</v>
+        <v>42.09731</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05056</v>
+        <v>0.05035</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8486</v>
+        <v>1.81703</v>
       </c>
     </row>
     <row r="10">
@@ -650,31 +660,51 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.54847</v>
+        <v>16.655</v>
       </c>
       <c r="D10" t="n">
-        <v>16.67498</v>
+        <v>16.53902</v>
       </c>
       <c r="E10" t="n">
-        <v>16.71619</v>
+        <v>16.57111</v>
       </c>
       <c r="F10" t="n">
-        <v>42.0418</v>
+        <v>42.36204</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04998</v>
+        <v>0.05124</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82425</v>
+        <v>1.85568</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -688,14 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60926</v>
+        <v>17.06536</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10564</v>
+        <v>16.47137</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.62011</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.65844</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05053</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.84308</v>
       </c>
     </row>
     <row r="13">
@@ -705,10 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5931999999999999</v>
+        <v>16.94199</v>
       </c>
       <c r="D13" t="n">
-        <v>1.12978</v>
+        <v>16.53326</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.73731</v>
+      </c>
+      <c r="F13" t="n">
+        <v>41.89249</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.8099</v>
       </c>
     </row>
     <row r="14">
@@ -718,10 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.61226</v>
+        <v>16.75284</v>
       </c>
       <c r="D14" t="n">
-        <v>1.09955</v>
+        <v>16.47049</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.7179</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.49069</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05092</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.85016</v>
       </c>
     </row>
     <row r="15">
@@ -731,10 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.60205</v>
+        <v>16.80079</v>
       </c>
       <c r="D15" t="n">
-        <v>1.11745</v>
+        <v>16.29176</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.59838</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.08269</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.05065</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.80582</v>
       </c>
     </row>
     <row r="16">
@@ -744,10 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.61224</v>
+        <v>16.76566</v>
       </c>
       <c r="D16" t="n">
-        <v>1.10462</v>
+        <v>16.17598</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.26223</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.44823</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.04987</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.75182</v>
       </c>
     </row>
     <row r="17">
@@ -757,10 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.60583</v>
+        <v>16.77312</v>
       </c>
       <c r="D17" t="n">
-        <v>1.11365</v>
+        <v>16.46667</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.59962</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.1222</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.83991</v>
       </c>
     </row>
     <row r="18">
@@ -770,10 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6110100000000001</v>
+        <v>16.84971</v>
       </c>
       <c r="D18" t="n">
-        <v>1.11229</v>
+        <v>16.58746</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.6582</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.13352</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05044</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.83362</v>
       </c>
     </row>
     <row r="19">
@@ -783,10 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.60179</v>
+        <v>16.71219</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1509</v>
+        <v>16.65662</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.69975</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.3221</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05058</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.78504</v>
       </c>
     </row>
     <row r="20">
@@ -796,51 +922,33 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.59928</v>
+        <v>17.18554</v>
       </c>
       <c r="D20" t="n">
-        <v>1.11798</v>
+        <v>16.41233</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.48427</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.92094</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05073</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.79605</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -852,32 +960,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.7496699999999999</v>
+        <v>0.61355</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0801</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.60097</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.96092</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.10917</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00755</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09223000000000001</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12868</v>
+        <v>1.10994</v>
       </c>
     </row>
     <row r="23">
@@ -887,28 +977,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.71979</v>
+        <v>0.6208399999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08205999999999999</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.61371</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.9745</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.10992</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00758</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09265</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12709</v>
+        <v>1.11814</v>
       </c>
     </row>
     <row r="24">
@@ -918,28 +990,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.7456</v>
+        <v>0.61004</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08273999999999999</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.58443</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.97814</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.10783</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00766</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09432</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12508</v>
+        <v>1.13951</v>
       </c>
     </row>
     <row r="25">
@@ -949,28 +1003,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.72759</v>
+        <v>0.60881</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08168</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.6126200000000001</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.96077</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.10966</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09379</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12574</v>
+        <v>1.13003</v>
       </c>
     </row>
     <row r="26">
@@ -980,28 +1016,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.75503</v>
+        <v>0.6153</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08211</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.61109</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.98892</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.10914</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00756</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09272</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12714</v>
+        <v>1.12038</v>
       </c>
     </row>
     <row r="27">
@@ -1011,28 +1029,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.75397</v>
+        <v>0.60578</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07915</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.61222</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.96994</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.11209</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09314</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12531</v>
+        <v>1.08946</v>
       </c>
     </row>
     <row r="28">
@@ -1042,28 +1042,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.75158</v>
+        <v>0.60009</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0809</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.60447</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.9648</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.10973</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00767</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.09079</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12877</v>
+        <v>1.1055</v>
       </c>
     </row>
     <row r="29">
@@ -1073,28 +1055,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.75026</v>
+        <v>0.61308</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0819</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.62196</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.96746</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.10968</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.00771</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.09131</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12773</v>
+        <v>1.12793</v>
       </c>
     </row>
     <row r="30">
@@ -1104,28 +1068,336 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.76226</v>
+        <v>0.60494</v>
       </c>
       <c r="D30" t="n">
-        <v>0.08116</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.59601</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.96511</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.11102</v>
-      </c>
-      <c r="H30" t="n">
+        <v>1.14056</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.74756</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08254</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.60067</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.95638</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.10738</v>
+      </c>
+      <c r="H32" t="n">
         <v>0.00759</v>
       </c>
-      <c r="I30" t="n">
-        <v>0.09490999999999999</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12422</v>
+      <c r="I32" t="n">
+        <v>0.09156</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12668</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7499400000000001</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08093</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.62409</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.95653</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.10891</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09258</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12708</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7451</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08108</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6132300000000001</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.92747</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.10863</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09526</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12684</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.74021</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08008999999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.60564</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.96168</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.11073</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00736</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09286</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12693</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.74627</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08089</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.60893</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.9492</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.0926</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12501</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.73929</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08233</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5950800000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.97979</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.11268</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09203</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12663</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.73449</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08151</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.61142</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.94381</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.11014</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09254</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12581</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.74157</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.07990999999999999</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.60794</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.96868</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.10858</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00756</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09365</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12661</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.7408</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.08144999999999999</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.60858</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.96366</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.10583</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.00748</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.09376</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.12723</v>
       </c>
     </row>
   </sheetData>
